--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0966B27F-8C3B-4008-8B9D-FA6551ED1726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FFC4B3-2213-4D20-8237-B2362CD277F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="fw release" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,7 +139,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head -&gt; Tail, Enable Line Delay, ID Check</t>
+    <t>Daisy 갯수 설정 가능 (CMD Model Select), pwm_res : 12Bit, ID Check (1 or 2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head -&gt; Tail, Enable Line Delay, ID Check (3이상이면 NG)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 04. 13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260413.hex</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,14 +565,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E10"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -684,6 +696,20 @@
         <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="3">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FFC4B3-2213-4D20-8237-B2362CD277F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86034B57-7E51-433B-BC4E-E3F6C20FAE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="fw release" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,6 +152,18 @@
   </si>
   <si>
     <t>xdic_led_module_control_bd_release_260413.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 04. 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260420.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen for : CH Dependency, SCAN No., Line Delay </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -201,12 +213,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -215,20 +242,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -565,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
@@ -594,13 +624,13 @@
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -608,38 +638,39 @@
       <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="3">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -647,13 +678,13 @@
       <c r="B7" s="3">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -661,13 +692,13 @@
       <c r="B8" s="3">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -675,13 +706,13 @@
       <c r="B9" s="3">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -689,13 +720,13 @@
       <c r="B10" s="3">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -703,14 +734,28 @@
       <c r="B11" s="3">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="4" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="3">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86034B57-7E51-433B-BC4E-E3F6C20FAE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC6AED-AE8B-430F-B1B4-E8C0DC006C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="fw release" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,6 +164,22 @@
   </si>
   <si>
     <t xml:space="preserve">Screen for : CH Dependency, SCAN No., Line Delay </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 06. 11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260611.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic의 serial latency 설정 변경 : 60 -&gt; 200, CMD_VERSION 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -595,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E12"/>
+  <dimension ref="B2:F13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
@@ -603,10 +619,11 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="1"/>
+    <col min="6" max="6" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,8 +636,11 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -633,8 +653,9 @@
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -647,8 +668,9 @@
       <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
@@ -659,8 +681,9 @@
         <v>9</v>
       </c>
       <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -673,8 +696,9 @@
       <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -687,8 +711,9 @@
       <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -701,8 +726,9 @@
       <c r="E8" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="3">
         <v>6</v>
       </c>
@@ -715,8 +741,9 @@
       <c r="E9" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="3">
         <v>7</v>
       </c>
@@ -729,8 +756,9 @@
       <c r="E10" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="3">
         <v>8</v>
       </c>
@@ -743,8 +771,9 @@
       <c r="E11" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="3">
         <v>9</v>
       </c>
@@ -756,6 +785,24 @@
       </c>
       <c r="E12" s="4" t="s">
         <v>32</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B13" s="3">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_fw_release.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC6AED-AE8B-430F-B1B4-E8C0DC006C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF87DEC2-4622-4886-B1AE-7086DED2F535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="fw release" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,6 +180,22 @@
   </si>
   <si>
     <t>Version Code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 07. 07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260707_XD_S.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.10 펌웨어와 변경 사항 없음; XD 개수에 따른 컴파일 구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260707_XD_D.hex</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -215,7 +231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,8 +244,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -252,13 +274,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -276,6 +324,18 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:F13"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
@@ -805,7 +865,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B14" s="6">
+        <v>11</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B15" s="6">
+        <v>12</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="7">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E14:E15"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
